--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:43</t>
+    <t xml:space="preserve">2026-09-09 22:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:30</t>
+    <t xml:space="preserve">2026-09-12 19:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
@@ -51,15 +51,15 @@
     <t xml:space="preserve">O'Higgins</t>
   </si>
   <si>
+    <t xml:space="preserve">Guaitecas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tortel</t>
   </si>
   <si>
     <t xml:space="preserve">Lago Verde</t>
   </si>
   <si>
-    <t xml:space="preserve">Guaitecas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Coyhaique</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:47</t>
+    <t xml:space="preserve">2026-09-24 00:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,7 +502,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>869</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +519,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>450</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4">
@@ -536,7 +536,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>275</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
@@ -544,16 +544,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>11201</v>
+        <v>11401</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>227</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -561,16 +561,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>11401</v>
+        <v>11302</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>137</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -578,16 +578,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>11302</v>
+        <v>11201</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -598,13 +598,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>11303</v>
+        <v>11203</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>8</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="9">
@@ -615,13 +615,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>11102</v>
+        <v>11303</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-3</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="10">
@@ -632,13 +632,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>11203</v>
+        <v>11102</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-145</v>
+        <v>-41</v>
       </c>
     </row>
     <row r="11">
@@ -655,7 +655,7 @@
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-782</v>
+        <v>-280</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:24</t>
+    <t xml:space="preserve">2026-09-27 22:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:13</t>
+    <t xml:space="preserve">2026-10-01 20:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:54</t>
+    <t xml:space="preserve">2026-10-02 13:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:21</t>
+    <t xml:space="preserve">2026-10-04 08:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:09</t>
+    <t xml:space="preserve">2026-10-05 08:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
